--- a/StructureDefinition-stroke-medication-administration-profile.xlsx
+++ b/StructureDefinition-stroke-medication-administration-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-medication-administration-profile.xlsx
+++ b/StructureDefinition-stroke-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-medication-administration-profile.xlsx
+++ b/StructureDefinition-stroke-medication-administration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="382">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1160,6 +1160,10 @@
   </si>
   <si>
     <t>If the administration is not instantaneous (rate is present), this can be specified to convey the total amount administered over period of time of a single administration.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -6644,7 +6648,7 @@
         <v>336</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>366</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
@@ -6653,18 +6657,18 @@
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6687,16 +6691,16 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6746,7 +6750,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6767,18 +6771,18 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6801,16 +6805,16 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6860,7 +6864,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6881,7 +6885,7 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-stroke-medication-administration-profile.xlsx
+++ b/StructureDefinition-stroke-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-medication-administration-profile.xlsx
+++ b/StructureDefinition-stroke-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-medication-administration-profile.xlsx
+++ b/StructureDefinition-stroke-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
